--- a/artfynd/A 63569-2023 artfynd.xlsx
+++ b/artfynd/A 63569-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63569-2023 artfynd.xlsx
+++ b/artfynd/A 63569-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>114438653</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -804,65 +799,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114438904</v>
+        <v>114446331</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Viesmosse, Vg</t>
+          <t>Gustavslyckan, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>341856</v>
+        <v>341716</v>
       </c>
       <c r="R3" t="n">
-        <v>6435796</v>
+        <v>6435878</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,24 +875,14 @@
           <t>2024-01-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-01-27</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rörde sig sjungande genom skogen. Tidigare 1 sj längre åt öster vid bäcken. Kan möjligen vara samma individ.</t>
+          <t>Vid basen på ett torrträd av en medelgrov gran utan bark fanns relativt färska spår efter spillkråkans födosök.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +897,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -936,16 +912,11 @@
         <v>114446470</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1048,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114446331</v>
+        <v>114438904</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,45 +1030,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gustavslyckan, nordost om, Vg</t>
+          <t>Viesmosse, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>341716</v>
+        <v>341856</v>
       </c>
       <c r="R5" t="n">
-        <v>6435878</v>
+        <v>6435796</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,14 +1099,24 @@
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-01-27</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid basen på ett torrträd av en medelgrov gran utan bark fanns relativt färska spår efter spillkråkans födosök.</t>
+          <t>Rörde sig sjungande genom skogen. Tidigare 1 sj längre åt öster vid bäcken. Kan möjligen vara samma individ.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,12 +1131,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 63569-2023 artfynd.xlsx
+++ b/artfynd/A 63569-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114438653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114446331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114446470</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,8 +1160,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114438904</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>